--- a/Data/Output/broken_enriched.xlsx
+++ b/Data/Output/broken_enriched.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -672,14 +672,18 @@
           <t>web_search_extract</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>http://www.astronautix.com/a/atlantis.html</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>height of Atlantis in Nowhere in meters above sea level</t>
+          <t>height of Atlantis in Nowhere meters</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -688,14 +692,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Atlantis» описує кілька об'єктів, узято найвідоміший; інші варіанти: 178 (Q3493630): Значення 4 менше за нижню межу 100 | [web_search_extract] Шлях через пошук вимагає ключа моделі (OPENAI_API_KEY), бо значення з тексту видачі витягає саме вона</t>
+          <t>[wikidata_lookup] Назва «Atlantis» неоднозначна; інші кандидати: 178 (Q3493630): Значення 4 менше за нижню межу 100 | [web_search_extract] Значення з пошукової видачі: Значення 37.24 менше за нижню межу 100</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>24</v>
+        <v>5124</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -773,7 +777,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -781,14 +785,18 @@
           <t>web_search_extract</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Olympus_Mons</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>height of Olympus Mons in Mars in meters above sea level</t>
+          <t>height of Olympus Mons in Mars meters</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -797,14 +805,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata: Значення 21229 більше за верхню межу 9000 | [web_search_extract] Шлях через пошук вимагає ключа моделі (OPENAI_API_KEY), бо значення з тексту видачі витягає саме вона</t>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata: Значення 21229 більше за верхню межу 9000 | [web_search_extract] Значення з пошукової видачі: Значення 21287 більше за верхню межу 9000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>4686</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -818,7 +826,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -826,10 +834,14 @@
           <t>web_search_extract</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/FactsThatWillBlowYourMind/videos/%EF%B8%8F-ever-wondered-why-your-keyboard-is-called-qwerty-its-not-random-the-layout-was/805675575386346</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>height of Qwerty Nonexistent Peak in Nowhere in meters above sea level</t>
+          <t>height of Qwerty Nonexistent Peak in Nowhere meters</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -842,14 +854,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Wikidata не має властивості P2044 для «Qwerty Nonexistent Peak» | [web_search_extract] Шлях через пошук вимагає ключа моделі (OPENAI_API_KEY), бо значення з тексту видачі витягає саме вона</t>
+          <t>[wikidata_lookup] Wikidata не має властивості P2044 для «Qwerty Nonexistent Peak» | [web_search_extract] У наведених результатах пошуку немає інформації про висоту Qwerty Nonexistent Peak in Nowhere.</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>27</v>
+        <v>5730</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Output/broken_enriched.xlsx
+++ b/Data/Output/broken_enriched.xlsx
@@ -464,6 +464,9 @@
           <t>Nowhere</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>4267</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -647,7 +650,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -662,6 +665,9 @@
           <t>height</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>4267</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>meters</t>
@@ -674,7 +680,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>http://www.astronautix.com/a/atlantis.html</t>
+          <t>https://en.wikipedia.org/wiki/Atlantis_Massif</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -687,16 +693,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>out_of_bounds</t>
+          <t>unconfirmed</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Atlantis» неоднозначна; інші кандидати: 178 (Q3493630): Значення 4 менше за нижню межу 100 | [web_search_extract] Значення з пошукової видачі: Значення 37.24 менше за нижню межу 100</t>
+          <t>[wikidata_lookup] Назва «Atlantis» неоднозначна; інші кандидати: 178 (Q3493630): Значення 4 менше за нижню межу 100 | [web_search_extract] Значення з пошукової видачі; контрольне джерело мовчить</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5124</v>
+        <v>5195</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -809,7 +815,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4686</v>
+        <v>2358</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -836,7 +842,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/FactsThatWillBlowYourMind/videos/%EF%B8%8F-ever-wondered-why-your-keyboard-is-called-qwerty-its-not-random-the-layout-was/805675575386346</t>
+          <t>https://www.instagram.com/reel/DRxIaj8CVLi?hl=en</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -858,7 +864,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5730</v>
+        <v>1631</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>

--- a/Data/Output/broken_enriched.xlsx
+++ b/Data/Output/broken_enriched.xlsx
@@ -527,20 +527,6 @@
   </sheetPr>
   <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -650,7 +636,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -698,11 +684,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Atlantis» неоднозначна; інші кандидати: 178 (Q3493630): Значення 4 менше за нижню межу 100 | [web_search_extract] Значення з пошукової видачі; контрольне джерело мовчить</t>
+          <t>[wikidata_lookup] Назва «Atlantis» неоднозначна: Значення 4 менше за мінімум 100 | [web_search_extract] Значення з пошукової видачі; контрольне джерело мовчить</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5195</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -730,7 +716,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>У рядку порожня вхідна колонка «Mountain»</t>
+          <t>Порожня вхідна колонка</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -762,7 +748,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Комірка вже заповнена, оригінальні дані не чіпаємо</t>
+          <t>Комірка вже заповнена</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -811,11 +797,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata: Значення 21229 більше за верхню межу 9000 | [web_search_extract] Значення з пошукової видачі: Значення 21287 більше за верхню межу 9000</t>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata: Значення 21229 більше за максимум 9000 | [web_search_extract] Значення з пошукової видачі: Значення 21287 більше за максимум 9000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2358</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -842,7 +828,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DRxIaj8CVLi?hl=en</t>
+          <t>https://en.wikipedia.org/wiki/QWERTY</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -860,11 +846,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Wikidata не має властивості P2044 для «Qwerty Nonexistent Peak» | [web_search_extract] У наведених результатах пошуку немає інформації про висоту Qwerty Nonexistent Peak in Nowhere.</t>
+          <t>[wikidata_lookup] Wikidata не має властивості P2044 для «Qwerty Nonexistent Peak» | [web_search_extract] Значення не знайдено в тексті</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1631</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
